--- a/data/codebook/codebook_v0.2.xlsx
+++ b/data/codebook/codebook_v0.2.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rb45b75d7799f48fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadatos" sheetId="2" r:id="R78a3bbc224fd4173"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conceptos" sheetId="3" r:id="R7b9af9f9ba984d34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rf7d6d197659349a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadatos" sheetId="2" r:id="R28f874d6bfa8403b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conceptos" sheetId="3" r:id="R9bc8020c79ec4744"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -646,6 +646,10 @@
       </x:c>
       <x:c r="B1" s="40"/>
     </x:row>
+    <x:row r="2">
+      <x:c r="A2"/>
+      <x:c r="B2"/>
+    </x:row>
     <x:row r="3" ht="38" customHeight="1">
       <x:c r="A3" s="47" t="str">
         <x:v>Aspecto</x:v>
@@ -723,7 +727,7 @@
         <x:v>Generar JSON</x:v>
       </x:c>
       <x:c r="B12" s="50" t="str">
-        <x:v>uv run python scripts/generate_codebook_json.py</x:v>
+        <x:v>uv run python -m features.manual_validation.generate_codebook_json</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="58" customHeight="1">
@@ -731,7 +735,7 @@
         <x:v>Comprobar sincronía</x:v>
       </x:c>
       <x:c r="B13" s="50" t="str">
-        <x:v>uv run python scripts/generate_codebook_json.py --check</x:v>
+        <x:v>uv run python -m features.manual_validation.generate_codebook_json --check</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="58" customHeight="1">
@@ -739,7 +743,7 @@
         <x:v>Iniciar interfaz</x:v>
       </x:c>
       <x:c r="B14" s="50" t="str">
-        <x:v>uv run python scripts/run_manual_validation.py</x:v>
+        <x:v>uv run python -m features.manual_validation</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="58" customHeight="1">
@@ -756,7 +760,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda3d4d3a525f4417"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R91b27d2ade2e4bb6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -825,7 +829,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf09f22c72754a18"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R75f7fda86da64c4c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1487,7 +1491,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf3af5f1b55394b42"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R283f0a91a76441a6"/>
   </x:tableParts>
 </x:worksheet>
 </file>